--- a/leave-tracker.xlsx
+++ b/leave-tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://capgemini-my.sharepoint.com/personal/nicketa_nicketa_capgemini_com/Documents/Work/2. POC/Specathon/Scrum-Master/Scrum-Master/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_F25DC773A252ABDACC104886619B6F9A5BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89B4C024-894D-4FEA-85A0-42752D598A45}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="11_F25DC773A252ABDACC104886619B6F9A5BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EB6EC1B-8148-478E-BD30-8526E81D8E6C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>Name</t>
   </si>
@@ -64,6 +64,9 @@
   </si>
   <si>
     <t>Manish</t>
+  </si>
+  <si>
+    <t>Sick</t>
   </si>
 </sst>
 </file>
@@ -452,7 +455,7 @@
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
